--- a/data_lake/industry/CFM/RDIMM.xlsx
+++ b/data_lake/industry/CFM/RDIMM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D97C82-F7D0-421F-914E-214179ADF3E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313D301E-1E08-CD47-A063-CC2E9993900D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="610" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17740" yWindow="780" windowWidth="18260" windowHeight="20700" tabRatio="610" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 RDIMM 16GB 3200" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="8">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -67,28 +67,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -126,46 +126,46 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -444,19 +444,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,7 +479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45846</v>
       </c>
@@ -502,7 +502,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45860</v>
       </c>
@@ -525,7 +525,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -548,7 +548,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45909</v>
       </c>
@@ -571,7 +571,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45944</v>
       </c>
@@ -594,7 +594,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45972</v>
       </c>
@@ -617,7 +617,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>46000</v>
       </c>
@@ -640,7 +640,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>46028</v>
       </c>
@@ -663,7 +663,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>46063</v>
       </c>
@@ -686,7 +686,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>46091</v>
       </c>
@@ -709,7 +709,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>46119</v>
       </c>
@@ -732,7 +732,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>46148</v>
       </c>
@@ -755,7 +755,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>46182</v>
       </c>
@@ -778,7 +778,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>46210</v>
       </c>
@@ -801,82 +801,114 @@
         <v>325</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10">
+        <v>150</v>
+      </c>
+      <c r="F16" s="10">
+        <v>400</v>
+      </c>
+      <c r="G16" s="10">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="10">
+        <v>150</v>
+      </c>
+      <c r="F17" s="10">
+        <v>400</v>
+      </c>
+      <c r="G17" s="10">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -890,19 +922,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7DCC6B8-7E19-4188-98AA-76DE911B494C}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -925,7 +957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45846</v>
       </c>
@@ -948,7 +980,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45860</v>
       </c>
@@ -971,7 +1003,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -994,7 +1026,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45909</v>
       </c>
@@ -1017,7 +1049,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45944</v>
       </c>
@@ -1040,7 +1072,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45972</v>
       </c>
@@ -1063,7 +1095,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>46000</v>
       </c>
@@ -1086,7 +1118,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>46028</v>
       </c>
@@ -1109,7 +1141,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>46063</v>
       </c>
@@ -1132,7 +1164,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>46091</v>
       </c>
@@ -1155,7 +1187,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>46119</v>
       </c>
@@ -1178,7 +1210,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>46148</v>
       </c>
@@ -1201,7 +1233,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>46182</v>
       </c>
@@ -1224,7 +1256,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>46210</v>
       </c>
@@ -1247,82 +1279,114 @@
         <v>485</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10">
+        <v>260</v>
+      </c>
+      <c r="F16" s="10">
+        <v>800</v>
+      </c>
+      <c r="G16" s="10">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="10">
+        <v>260</v>
+      </c>
+      <c r="F17" s="10">
+        <v>800</v>
+      </c>
+      <c r="G17" s="10">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1336,19 +1400,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C05E61F2-2635-4C27-8DCB-93976B9195D8}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.69921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1371,7 +1435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45846</v>
       </c>
@@ -1394,7 +1458,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45860</v>
       </c>
@@ -1417,7 +1481,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -1440,7 +1504,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45909</v>
       </c>
@@ -1463,7 +1527,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45944</v>
       </c>
@@ -1486,7 +1550,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45972</v>
       </c>
@@ -1509,7 +1573,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>46000</v>
       </c>
@@ -1532,7 +1596,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>46028</v>
       </c>
@@ -1555,7 +1619,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>46063</v>
       </c>
@@ -1578,7 +1642,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>46091</v>
       </c>
@@ -1601,7 +1665,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>46119</v>
       </c>
@@ -1624,7 +1688,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>46148</v>
       </c>
@@ -1647,7 +1711,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>46182</v>
       </c>
@@ -1670,7 +1734,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>46210</v>
       </c>
@@ -1693,82 +1757,114 @@
         <v>850</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10">
+        <v>550</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1300</v>
+      </c>
+      <c r="G16" s="10">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="10">
+        <v>550</v>
+      </c>
+      <c r="F17" s="10">
+        <v>1300</v>
+      </c>
+      <c r="G17" s="10">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -1782,19 +1878,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BBC2934-9EA8-4CA1-881F-5F7DC593D698}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.69921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1817,7 +1913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45846</v>
       </c>
@@ -1840,7 +1936,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45860</v>
       </c>
@@ -1863,7 +1959,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -1886,7 +1982,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45909</v>
       </c>
@@ -1909,7 +2005,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45944</v>
       </c>
@@ -1932,7 +2028,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45972</v>
       </c>
@@ -1955,7 +2051,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>46000</v>
       </c>
@@ -1978,7 +2074,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>46028</v>
       </c>
@@ -2001,7 +2097,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>46063</v>
       </c>
@@ -2024,7 +2120,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>46091</v>
       </c>
@@ -2047,7 +2143,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>46119</v>
       </c>
@@ -2070,7 +2166,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>46148</v>
       </c>
@@ -2093,7 +2189,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>46182</v>
       </c>
@@ -2116,7 +2212,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>46210</v>
       </c>
@@ -2139,82 +2235,114 @@
         <v>730</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10">
+        <v>880</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1800</v>
+      </c>
+      <c r="G16" s="10">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="10">
+        <v>900</v>
+      </c>
+      <c r="F17" s="10">
+        <v>2100</v>
+      </c>
+      <c r="G17" s="10">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -2228,18 +2356,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29FF9896-5884-4059-8248-612FA72E9D05}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2262,7 +2390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45846</v>
       </c>
@@ -2285,7 +2413,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45860</v>
       </c>
@@ -2308,7 +2436,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -2331,7 +2459,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45909</v>
       </c>
@@ -2354,7 +2482,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45944</v>
       </c>
@@ -2377,7 +2505,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45972</v>
       </c>
@@ -2400,7 +2528,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>46000</v>
       </c>
@@ -2423,7 +2551,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>46028</v>
       </c>
@@ -2446,7 +2574,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>46063</v>
       </c>
@@ -2469,7 +2597,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>46091</v>
       </c>
@@ -2492,7 +2620,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>46119</v>
       </c>
@@ -2515,7 +2643,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>46148</v>
       </c>
@@ -2538,7 +2666,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>46182</v>
       </c>
@@ -2561,7 +2689,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>46210</v>
       </c>
@@ -2584,82 +2712,114 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1560</v>
+      </c>
+      <c r="F16" s="10">
+        <v>3300</v>
+      </c>
+      <c r="G16" s="10">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1560</v>
+      </c>
+      <c r="F17" s="10">
+        <v>3300</v>
+      </c>
+      <c r="G17" s="10">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -2673,18 +2833,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1879A24C-F295-4F90-921D-1BCFB04E666C}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2707,7 +2867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>45846</v>
       </c>
@@ -2730,7 +2890,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>45860</v>
       </c>
@@ -2753,7 +2913,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>45874</v>
       </c>
@@ -2776,7 +2936,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>45909</v>
       </c>
@@ -2799,7 +2959,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>45944</v>
       </c>
@@ -2822,7 +2982,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>45972</v>
       </c>
@@ -2845,7 +3005,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>46000</v>
       </c>
@@ -2868,7 +3028,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>46028</v>
       </c>
@@ -2891,7 +3051,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>46063</v>
       </c>
@@ -2914,7 +3074,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>46091</v>
       </c>
@@ -2937,7 +3097,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>46119</v>
       </c>
@@ -2960,7 +3120,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>46148</v>
       </c>
@@ -2983,7 +3143,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>46182</v>
       </c>
@@ -3006,7 +3166,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>46210</v>
       </c>
@@ -3029,82 +3189,114 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46245</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10">
+        <v>2520</v>
+      </c>
+      <c r="F16" s="10">
+        <v>3900</v>
+      </c>
+      <c r="G16" s="10">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46273</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="10">
+        <v>2550</v>
+      </c>
+      <c r="F17" s="10">
+        <v>3500</v>
+      </c>
+      <c r="G17" s="10">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="10"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
